--- a/tiflow-chargeitem/build/0.9.0/StructureDefinition-GEM-ERPCHRG-PR-Consent.xlsx
+++ b/tiflow-chargeitem/build/0.9.0/StructureDefinition-GEM-ERPCHRG-PR-Consent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3553" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}ppc-4:IF Scope=adr, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='adr').exists().not()}ppc-5:IF Scope=treatment, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='treatment').exists().not()}ppc-2:IF Scope=privacy, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='patient-privacy').exists().not()}ppc-3:IF Scope=research, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='research').exists().not()}ppc-1:Either a Policy or PolicyRule {policy.exists() or policyRule.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}ppc-1:Either a Policy or PolicyRule {policy.exists() or policyRule.exists()}ppc-2:IF Scope=privacy, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='patient-privacy').exists().not()}ppc-3:IF Scope=research, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='research').exists().not()}ppc-4:IF Scope=adr, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='adr').exists().not()}ppc-5:IF Scope=treatment, there must be a patient {patient.exists() or scope.coding.where(system='something' and code='treatment').exists().not()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -497,16 +497,6 @@
   </si>
   <si>
     <t>Meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
   </si>
   <si>
     <t>Consent.meta.tag</t>
@@ -678,9 +668,6 @@
     <t>Event.identifier</t>
   </si>
   <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
     <t>.id</t>
   </si>
   <si>
@@ -739,21 +726,12 @@
     <t>A selector of the type of consent being presented: ADR, Privacy, Treatment, Research.  This list is now extensible.</t>
   </si>
   <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
     <t>The four anticipated uses for the Consent Resource.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Consent.scope.id</t>
   </si>
   <si>
@@ -869,9 +847,6 @@
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
@@ -979,10 +954,6 @@
   </si>
   <si>
     <t>Commonly, the patient the consent pertains to is the author, but for young and old people, it may be some other person.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1209,15 +1180,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>CX.7 + CX.8</t>
@@ -1342,9 +1305,6 @@
     <t>Field 24/ ConsenterID</t>
   </si>
   <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
-  </si>
-  <si>
     <t>FiveWs.actor</t>
   </si>
   <si>
@@ -1365,9 +1325,6 @@
     <t>The organization that manages the consent, and the framework within which it is executed.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>FiveWs.witness</t>
   </si>
   <si>
@@ -1435,9 +1392,6 @@
     <t>Entity or Organization having regulatory jurisdiction or accountability for  enforcing policies pertaining to Consent Directives.</t>
   </si>
   <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
-  </si>
-  <si>
     <t xml:space="preserve">ppc-1
 </t>
   </si>
@@ -1469,10 +1423,6 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
   </si>
   <si>
-    <t>ele-1
-ppc-1</t>
-  </si>
-  <si>
     <t>Consent.verification</t>
   </si>
   <si>
@@ -1562,12 +1512,6 @@
   </si>
   <si>
     <t>The timeframe in this rule is valid.</t>
-  </si>
-  <si>
-    <t>DR</t>
-  </si>
-  <si>
-    <t>IVL&lt;TS&gt;[lowClosed="true" and highClosed="true"] or URG&lt;TS&gt;[lowClosed="true" and highClosed="true"]</t>
   </si>
   <si>
     <t>Consent.provision.actor</t>
@@ -2127,7 +2071,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.8203125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="87.9765625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -3488,7 +3432,7 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>99</v>
@@ -3497,10 +3441,10 @@
         <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>75</v>
@@ -3508,10 +3452,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3537,13 +3481,13 @@
         <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3569,31 +3513,31 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3602,7 +3546,7 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>99</v>
@@ -3611,10 +3555,10 @@
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>75</v>
@@ -3622,10 +3566,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3651,13 +3595,13 @@
         <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3707,7 +3651,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3736,10 +3680,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3762,16 +3706,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3797,31 +3741,31 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3850,14 +3794,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3876,16 +3820,16 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3935,7 +3879,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3956,7 +3900,7 @@
         <v>75</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>75</v>
@@ -3964,14 +3908,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3990,16 +3934,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4049,7 +3993,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -4070,7 +4014,7 @@
         <v>75</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>75</v>
@@ -4078,10 +4022,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4110,7 +4054,7 @@
         <v>109</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>111</v>
@@ -4151,19 +4095,19 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4184,7 +4128,7 @@
         <v>75</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>75</v>
@@ -4192,10 +4136,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4221,16 +4165,16 @@
         <v>108</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -4267,19 +4211,19 @@
         <v>75</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4300,7 +4244,7 @@
         <v>75</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>75</v>
@@ -4308,10 +4252,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4334,16 +4278,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4357,7 +4301,7 @@
         <v>75</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>75</v>
@@ -4393,7 +4337,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4402,30 +4346,30 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4448,26 +4392,26 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>75</v>
@@ -4485,13 +4429,13 @@
         <v>75</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>75</v>
@@ -4509,7 +4453,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>87</v>
@@ -4524,24 +4468,24 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4564,17 +4508,15 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>75</v>
@@ -4602,10 +4544,10 @@
         <v>151</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>75</v>
@@ -4623,7 +4565,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>87</v>
@@ -4632,7 +4574,7 @@
         <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>99</v>
@@ -4641,10 +4583,10 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>234</v>
+        <v>75</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>235</v>
+        <v>75</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>75</v>
@@ -4652,10 +4594,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4764,10 +4706,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4878,10 +4820,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4907,16 +4849,16 @@
         <v>147</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
@@ -4965,7 +4907,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4974,7 +4916,7 @@
         <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>99</v>
@@ -4983,10 +4925,10 @@
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>75</v>
@@ -4994,10 +4936,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5106,10 +5048,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5220,10 +5162,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5249,23 +5191,23 @@
         <v>129</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>75</v>
@@ -5307,7 +5249,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -5325,10 +5267,10 @@
         <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>75</v>
@@ -5336,10 +5278,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5365,13 +5307,13 @@
         <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5421,7 +5363,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5439,10 +5381,10 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>75</v>
@@ -5450,10 +5392,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5476,24 +5418,24 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>75</v>
@@ -5535,7 +5477,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5553,10 +5495,10 @@
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>75</v>
@@ -5564,10 +5506,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5593,23 +5535,21 @@
         <v>101</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>75</v>
@@ -5651,7 +5591,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5669,10 +5609,10 @@
         <v>75</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>75</v>
@@ -5680,10 +5620,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5706,19 +5646,19 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>75</v>
@@ -5767,7 +5707,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5785,10 +5725,10 @@
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>75</v>
@@ -5796,10 +5736,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5825,16 +5765,16 @@
         <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -5883,7 +5823,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5901,10 +5841,10 @@
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>75</v>
@@ -5912,10 +5852,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5938,17 +5878,15 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5973,11 +5911,11 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5995,7 +5933,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -6004,30 +5942,30 @@
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6050,16 +5988,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6109,7 +6047,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6118,30 +6056,30 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>311</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6250,10 +6188,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6364,10 +6302,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6393,13 +6331,13 @@
         <v>101</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6449,7 +6387,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -6458,7 +6396,7 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>99</v>
@@ -6470,7 +6408,7 @@
         <v>75</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>75</v>
@@ -6478,10 +6416,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6507,13 +6445,13 @@
         <v>129</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6542,10 +6480,10 @@
         <v>151</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>75</v>
@@ -6563,7 +6501,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6584,7 +6522,7 @@
         <v>75</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
@@ -6592,10 +6530,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6618,16 +6556,16 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6677,7 +6615,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6686,7 +6624,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -6695,10 +6633,10 @@
         <v>75</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>75</v>
@@ -6706,10 +6644,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6818,10 +6756,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6932,10 +6870,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6958,19 +6896,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -6995,13 +6933,13 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -7019,7 +6957,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7037,10 +6975,10 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>75</v>
@@ -7048,10 +6986,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7074,19 +7012,19 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -7096,7 +7034,7 @@
         <v>75</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>75</v>
@@ -7114,10 +7052,10 @@
         <v>151</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -7135,7 +7073,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7144,19 +7082,19 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>75</v>
@@ -7164,10 +7102,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7193,29 +7131,29 @@
         <v>129</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>75</v>
@@ -7251,7 +7189,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7269,10 +7207,10 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>75</v>
@@ -7280,10 +7218,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7309,13 +7247,13 @@
         <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7329,7 +7267,7 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>75</v>
@@ -7365,7 +7303,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7377,16 +7315,16 @@
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>75</v>
@@ -7394,10 +7332,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7420,17 +7358,15 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -7479,7 +7415,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7488,19 +7424,19 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>384</v>
+        <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
@@ -7508,10 +7444,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7534,16 +7470,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7593,7 +7529,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7602,19 +7538,19 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>311</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>75</v>
@@ -7622,10 +7558,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7734,10 +7670,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7848,10 +7784,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7877,13 +7813,13 @@
         <v>101</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7933,7 +7869,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7942,7 +7878,7 @@
         <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>99</v>
@@ -7954,7 +7890,7 @@
         <v>75</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>75</v>
@@ -7962,10 +7898,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7991,13 +7927,13 @@
         <v>129</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8026,10 +7962,10 @@
         <v>151</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -8047,7 +7983,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -8068,7 +8004,7 @@
         <v>75</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>75</v>
@@ -8076,10 +8012,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8102,16 +8038,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8161,7 +8097,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8170,7 +8106,7 @@
         <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>99</v>
@@ -8179,10 +8115,10 @@
         <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>75</v>
@@ -8190,10 +8126,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8219,13 +8155,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8275,7 +8211,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8296,7 +8232,7 @@
         <v>75</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>75</v>
@@ -8304,10 +8240,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8333,13 +8269,13 @@
         <v>101</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8389,7 +8325,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8410,7 +8346,7 @@
         <v>75</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>75</v>
@@ -8418,10 +8354,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8444,16 +8380,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8503,7 +8439,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8518,28 +8454,28 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8558,16 +8494,16 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8617,7 +8553,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8626,34 +8562,34 @@
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>311</v>
+        <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>424</v>
+        <v>75</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8672,17 +8608,15 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>75</v>
@@ -8731,7 +8665,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8740,30 +8674,30 @@
         <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>311</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>424</v>
+        <v>75</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>432</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8786,16 +8720,16 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8845,7 +8779,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8854,7 +8788,7 @@
         <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>99</v>
@@ -8863,10 +8797,10 @@
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>75</v>
@@ -8874,10 +8808,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8900,13 +8834,13 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8957,7 +8891,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8966,7 +8900,7 @@
         <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>99</v>
@@ -8978,7 +8912,7 @@
         <v>75</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>75</v>
@@ -8986,10 +8920,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9098,10 +9032,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9171,16 +9105,16 @@
         <v>75</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>115</v>
@@ -9212,14 +9146,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9241,16 +9175,16 @@
         <v>108</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>75</v>
@@ -9299,7 +9233,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9320,7 +9254,7 @@
         <v>75</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>75</v>
@@ -9328,10 +9262,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9357,14 +9291,12 @@
         <v>129</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -9413,7 +9345,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9422,7 +9354,7 @@
         <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>99</v>
@@ -9442,10 +9374,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9471,13 +9403,13 @@
         <v>129</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9527,7 +9459,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9536,7 +9468,7 @@
         <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>99</v>
@@ -9556,10 +9488,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9582,19 +9514,19 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -9619,11 +9551,11 @@
         <v>75</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>75</v>
@@ -9641,7 +9573,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -9650,7 +9582,7 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>99</v>
@@ -9659,10 +9591,10 @@
         <v>75</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>234</v>
+        <v>75</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>235</v>
+        <v>75</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>75</v>
@@ -9670,10 +9602,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9696,13 +9628,13 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9753,7 +9685,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9762,7 +9694,7 @@
         <v>77</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>99</v>
@@ -9774,7 +9706,7 @@
         <v>75</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>75</v>
@@ -9782,10 +9714,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9894,10 +9826,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9967,16 +9899,16 @@
         <v>75</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>115</v>
@@ -10008,14 +9940,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10037,16 +9969,16 @@
         <v>108</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -10095,7 +10027,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10116,7 +10048,7 @@
         <v>75</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>75</v>
@@ -10124,10 +10056,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10150,13 +10082,13 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10207,7 +10139,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>87</v>
@@ -10236,10 +10168,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10262,17 +10194,15 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -10321,7 +10251,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10330,10 +10260,10 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>311</v>
+        <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
@@ -10342,7 +10272,7 @@
         <v>75</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>424</v>
+        <v>75</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>75</v>
@@ -10350,10 +10280,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10376,13 +10306,13 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10433,7 +10363,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10462,10 +10392,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10488,13 +10418,13 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10545,7 +10475,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10554,7 +10484,7 @@
         <v>87</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>99</v>
@@ -10566,7 +10496,7 @@
         <v>75</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>75</v>
@@ -10574,10 +10504,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10686,10 +10616,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10759,16 +10689,16 @@
         <v>75</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>115</v>
@@ -10800,14 +10730,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10829,16 +10759,16 @@
         <v>108</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>75</v>
@@ -10887,7 +10817,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10908,7 +10838,7 @@
         <v>75</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>75</v>
@@ -10916,10 +10846,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10942,13 +10872,13 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10975,13 +10905,13 @@
         <v>75</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>75</v>
@@ -10999,7 +10929,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11028,10 +10958,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11054,17 +10984,15 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>75</v>
@@ -11113,7 +11041,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11122,19 +11050,19 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>384</v>
+        <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>495</v>
+        <v>75</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>496</v>
+        <v>75</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>75</v>
@@ -11142,10 +11070,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11168,13 +11096,13 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11182,7 +11110,7 @@
         <v>75</v>
       </c>
       <c r="Q80" t="s" s="2">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="R80" t="s" s="2">
         <v>75</v>
@@ -11227,7 +11155,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11236,7 +11164,7 @@
         <v>77</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>99</v>
@@ -11248,7 +11176,7 @@
         <v>75</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>75</v>
@@ -11256,10 +11184,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11368,10 +11296,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11441,16 +11369,16 @@
         <v>75</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>115</v>
@@ -11482,14 +11410,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11511,16 +11439,16 @@
         <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>75</v>
@@ -11569,7 +11497,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11590,7 +11518,7 @@
         <v>75</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>75</v>
@@ -11598,10 +11526,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11624,17 +11552,15 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>75</v>
@@ -11662,10 +11588,10 @@
         <v>151</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>75</v>
@@ -11683,7 +11609,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>87</v>
@@ -11692,7 +11618,7 @@
         <v>87</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>99</v>
@@ -11701,10 +11627,10 @@
         <v>75</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>234</v>
+        <v>75</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>235</v>
+        <v>75</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>75</v>
@@ -11712,10 +11638,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11738,17 +11664,15 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>75</v>
@@ -11797,7 +11721,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>87</v>
@@ -11806,10 +11730,10 @@
         <v>87</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>311</v>
+        <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>75</v>
@@ -11818,7 +11742,7 @@
         <v>75</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>424</v>
+        <v>75</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>75</v>
@@ -11826,10 +11750,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11852,23 +11776,23 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q86" t="s" s="2">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="R86" t="s" s="2">
         <v>75</v>
@@ -11889,13 +11813,13 @@
         <v>75</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>75</v>
@@ -11913,7 +11837,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -11922,7 +11846,7 @@
         <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>99</v>
@@ -11931,10 +11855,10 @@
         <v>75</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>234</v>
+        <v>75</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>235</v>
+        <v>75</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>75</v>
@@ -11942,10 +11866,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11971,13 +11895,13 @@
         <v>147</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12027,7 +11951,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12036,7 +11960,7 @@
         <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>99</v>
@@ -12045,10 +11969,10 @@
         <v>75</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>75</v>
@@ -12056,10 +11980,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12085,13 +12009,13 @@
         <v>147</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12120,10 +12044,10 @@
         <v>151</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>75</v>
@@ -12141,7 +12065,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12150,7 +12074,7 @@
         <v>77</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>99</v>
@@ -12159,10 +12083,10 @@
         <v>75</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>75</v>
@@ -12170,10 +12094,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12199,13 +12123,13 @@
         <v>147</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12234,10 +12158,10 @@
         <v>151</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>75</v>
@@ -12255,7 +12179,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12264,7 +12188,7 @@
         <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>99</v>
@@ -12273,10 +12197,10 @@
         <v>75</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>75</v>
@@ -12284,10 +12208,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12310,16 +12234,16 @@
         <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12345,13 +12269,13 @@
         <v>75</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>75</v>
@@ -12369,7 +12293,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12378,7 +12302,7 @@
         <v>77</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>99</v>
@@ -12387,10 +12311,10 @@
         <v>75</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>234</v>
+        <v>75</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>235</v>
+        <v>75</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>75</v>
@@ -12398,10 +12322,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12424,16 +12348,16 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12483,7 +12407,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12492,19 +12416,19 @@
         <v>87</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>384</v>
+        <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>495</v>
+        <v>75</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>496</v>
+        <v>75</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>75</v>
@@ -12512,10 +12436,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12538,13 +12462,13 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>547</v>
+        <v>530</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12552,7 +12476,7 @@
         <v>75</v>
       </c>
       <c r="Q92" t="s" s="2">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="R92" t="s" s="2">
         <v>75</v>
@@ -12597,7 +12521,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12606,7 +12530,7 @@
         <v>77</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>99</v>
@@ -12618,7 +12542,7 @@
         <v>75</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>75</v>
@@ -12626,10 +12550,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12738,10 +12662,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12811,16 +12735,16 @@
         <v>75</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>115</v>
@@ -12852,14 +12776,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -12881,16 +12805,16 @@
         <v>108</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -12939,7 +12863,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -12960,7 +12884,7 @@
         <v>75</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>75</v>
@@ -12968,10 +12892,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12994,13 +12918,13 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13027,13 +12951,13 @@
         <v>75</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>75</v>
@@ -13051,7 +12975,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>87</v>
@@ -13080,10 +13004,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13106,17 +13030,15 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>75</v>
@@ -13165,7 +13087,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>87</v>
@@ -13174,10 +13096,10 @@
         <v>87</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>155</v>
+        <v>75</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>311</v>
+        <v>99</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>75</v>
@@ -13186,7 +13108,7 @@
         <v>75</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>424</v>
+        <v>75</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>75</v>
@@ -13194,10 +13116,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13223,10 +13145,10 @@
         <v>78</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13277,7 +13199,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13289,7 +13211,7 @@
         <v>75</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>75</v>
